--- a/artfynd/A 68108-2019 artfynd.xlsx
+++ b/artfynd/A 68108-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68108-2019 artfynd.xlsx
+++ b/artfynd/A 68108-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106075275</v>
       </c>
       <c r="B2" t="n">
-        <v>77595</v>
+        <v>78615</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688327.3183669511</v>
+        <v>688327</v>
       </c>
       <c r="R2" t="n">
-        <v>6606691.384480706</v>
+        <v>6606691</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>

--- a/artfynd/A 68108-2019 artfynd.xlsx
+++ b/artfynd/A 68108-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106075275</v>
       </c>
       <c r="B2" t="n">
-        <v>78615</v>
+        <v>78631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
